--- a/stories/arbres/ATOM-FAM.AID.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Hippolyte dit : maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal. Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
+          <t>Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal. Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon.
+enfant-m|Maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal.
+narrateur|Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1488,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
     </row>
@@ -1629,6 +1657,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1787,6 +1820,11 @@
         <v>12</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hippolyte pose une noix. Maman s'assoit près de lui.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1949,6 +1987,11 @@
         <v>12</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1967,7 +2010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1984,6 +2027,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-08.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1312,6 +1317,7 @@
 narrateur|Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1495,6 +1501,7 @@
           <t>narrateur|Hippolyte n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1662,6 +1669,7 @@
           <t>narrateur|Hippolyte a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1833,7 @@
           <t>narrateur|Hippolyte pose une noix. Maman s'assoit près de lui.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1992,6 +2001,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2010,7 +2020,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2034,6 +2044,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2048,7 +2072,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2235,6 +2259,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-FAM.AID.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-08.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hippolyte appelle maman</t>
+          <t>La noix de Chouchou</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une noix roule sous la chaise. Chouchou veut le bocal, trop haut. Il va vers maman et dit le besoin. Maman donne le bocal. Les noix sentent bon.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal. Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
+          <t>Une noix roule sous la chaise. Elle fait un petit bruit. La cuisine est tiède. Le rideau beige ne bouge pas. Ça sent le bois et le pain. Une tasse bleue attend sur la table. Papa range une assiette. Maman est dans le salon. Tu as vu la noix, Chouchou ? Elle a roulé. Oui. Tout doucement. En ce moment, Chouchou lève les yeux. Il veut le bocal. Le bocal est en haut. Trop haut. Le verre brille un peu. Je veux le bocal, papa. Il est trop haut. Chouchou lève les bras. Il n'arrive pas. C'est trop difficile. Chouchou va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Le canapé est mou. Maman. J'ai besoin du bocal. Je t'écoute, Chouchou. Tu as dit le besoin. Maman vient. Maman donne le bocal. Le bocal est lourd. Les noix sentent bon. Merci, maman. Bravo. Tu es venu vers moi. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Chouchou ouvre le bocal. Une noix est lisse. Une noix est un peu rêche. Tu poses une noix ? Oui, maman. Chouchou pose une noix. Elle fait un petit bruit. C'est la même noix ? Non. Une autre. Tu as dit le besoin. Le bocal est là. Le rideau beige ne bouge pas. La tasse bleue attend encore. Tu veux un peu d'eau ? Oui. L'eau est fraîche. Chouchou boit une gorgée. La noix sous la chaise, tu la prends ? Oui, papa. Chouchou ramasse la noix. Elle est ronde et un peu froide. Tu la mets avec les autres ? Oui, maman. Chouchou pose la noix dans le bocal. Ça fait un petit bruit. Bravo, Chouchou. Tu as dit le besoin. Le bocal est là.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,12 +1324,74 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon.
-enfant-m|Maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal.
-narrateur|Les noix sentent bon. Hippolyte dit merci. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une noix roule sous la chaise.
+narrateur|Elle fait un petit bruit.
+narrateur|La cuisine est tiède.
+narrateur|Le rideau beige ne bouge pas.
+narrateur|Ça sent le bois et le pain.
+narrateur|Une tasse bleue attend sur la table.
+narrateur|Papa range une assiette.
+narrateur|Maman est dans le salon.
+papa|Tu as vu la noix, Chouchou ?
+enfant-m|Elle a roulé.
+papa|Oui. Tout doucement.
+narrateur|En ce moment, Chouchou lève les yeux.
+narrateur|Il veut le bocal.
+narrateur|Le bocal est en haut.
+narrateur|Trop haut.
+narrateur|Le verre brille un peu.
+enfant-m|Je veux le bocal, papa.
+papa|Il est trop haut.
+narrateur|Chouchou lève les bras.
+narrateur|Il n'arrive pas.
+narrateur|C'est trop difficile.
+narrateur|Chouchou va vers la porte.
+narrateur|Il va vers eux.
+narrateur|Il va vers maman.
+narrateur|Maman est dans le salon.
+narrateur|Le canapé est mou.
+enfant-m|Maman. J'ai besoin du bocal.
+maman|Je t'écoute, Chouchou.
+maman|Tu as dit le besoin.
+narrateur|Maman vient.
+narrateur|Maman donne le bocal.
+narrateur|Le bocal est lourd.
+narrateur|Les noix sentent bon.
+enfant-m|Merci, maman.
+maman|Bravo. Tu es venu vers moi.
+papa|On peut aller vers eux.
+maman|On peut dire le besoin.
+papa|On peut appeler papa ou maman.
+narrateur|Chouchou ouvre le bocal.
+narrateur|Une noix est lisse.
+narrateur|Une noix est un peu rêche.
+maman|Tu poses une noix ?
+enfant-m|Oui, maman.
+narrateur|Chouchou pose une noix.
+narrateur|Elle fait un petit bruit.
+papa|C'est la même noix ?
+enfant-m|Non. Une autre.
+maman|Tu as dit le besoin.
+papa|Le bocal est là.
+narrateur|Le rideau beige ne bouge pas.
+narrateur|La tasse bleue attend encore.
+maman|Tu veux un peu d'eau ?
+enfant-m|Oui.
+narrateur|L'eau est fraîche.
+narrateur|Chouchou boit une gorgée.
+papa|La noix sous la chaise, tu la prends ?
+enfant-m|Oui, papa.
+narrateur|Chouchou ramasse la noix.
+narrateur|Elle est ronde et un peu froide.
+maman|Tu la mets avec les autres ?
+enfant-m|Oui, maman.
+narrateur|Chouchou pose la noix dans le bocal.
+narrateur|Ça fait un petit bruit.
+papa|Bravo, Chouchou.
+maman|Tu as dit le besoin.
+maman|Le bocal est là.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1342,7 +1416,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte n'arrive pas. Que fait-il ?</t>
+          <t>Chouchou n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1498,10 +1572,10 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte n'arrive pas. Que fait-il ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Chouchou n'arrive pas.
+narrateur|Que fait-il ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1526,7 +1600,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là.</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là. Tu es venu me le dire. Bravo. C'est du bon travail, Chouchou. Tu as fini ta noix ? Oui, papa. La noix sous la chaise est encore là. Elle ne roule plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1666,10 +1740,19 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Chouchou a appelé.
+narrateur|Il a dit le besoin.
+narrateur|Maman a entendu.
+narrateur|Le bocal est là.
+maman|Tu es venu me le dire.
+maman|Bravo.
+papa|C'est du bon travail, Chouchou.
+papa|Tu as fini ta noix ?
+enfant-m|Oui, papa.
+narrateur|La noix sous la chaise est encore là.
+narrateur|Elle ne roule plus.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1694,7 +1777,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hippolyte pose une noix. Maman s'assoit près de lui.</t>
+          <t>Chouchou pose une noix. Maman s'assoit près de lui. Elle est lisse ? Oui. Lisse. On range le bocal après ? Oui, papa. Le bocal est lourd. Les noix sentent encore bon. On reste un peu ensemble ? Oui. La cuisine est tiède. La tasse bleue brille. On referme le bocal ensemble ? Oui, papa. Papa tient le bocal. Chouchou pose le couvercle. C'est bien. On a fini.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1830,10 +1913,25 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hippolyte pose une noix. Maman s'assoit près de lui.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Chouchou pose une noix.
+narrateur|Maman s'assoit près de lui.
+maman|Elle est lisse ?
+enfant-m|Oui. Lisse.
+papa|On range le bocal après ?
+enfant-m|Oui, papa.
+narrateur|Le bocal est lourd.
+narrateur|Les noix sentent encore bon.
+maman|On reste un peu ensemble ?
+enfant-m|Oui.
+narrateur|La cuisine est tiède.
+narrateur|La tasse bleue brille.
+papa|On referme le bocal ensemble ?
+enfant-m|Oui, papa.
+narrateur|Papa tient le bocal.
+narrateur|Chouchou pose le couvercle.
+maman|C'est bien. On a fini.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1858,7 +1956,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Chouchou. Tu as fait du bon travail. La noix ne roule plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -1998,10 +2096,14 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>enfant-m|J'ai dit le besoin.
+maman|Oui. Tu es venu vers moi.
+papa|Bravo, Chouchou.
+papa|Tu as fait du bon travail.
+narrateur|La noix ne roule plus.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2020,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2058,6 +2160,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-08.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hippolyte est dans la cuisine. Il veut le bocal. Le bocal est en haut. Trop haut. Hippolyte lève les bras. Il n'arrive pas. Hippolyte va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Hippolyte dit : maman. J'ai besoin du bocal. Il dit le besoin. Maman écoute. Maman vient. Maman donne le bocal. Les noix sentent bon. Hippolyte dit merci. On peut &lt;emphasis level="moderate"&gt;aller&lt;/emphasis&gt; vers eux. On peut dire le besoin. On peut appeler papa ou maman. Maman sourit. Hippolyte ouvre le bocal.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Une noix roule sous la chaise. Elle fait un petit bruit. La cuisine est tiède. Le rideau beige ne bouge pas. Ça sent le bois et le pain. Une tasse bleue attend sur la table. Papa range une assiette. Maman est dans le salon. Tu as vu la noix, Chouchou ? Elle a roulé. Oui. Tout doucement. En ce moment, Chouchou lève les yeux. Il veut le bocal. Le bocal est en haut. Trop haut. Le verre brille un peu. Je veux le bocal, papa. Il est trop haut. Chouchou lève les bras. Il n'arrive pas. C'est trop difficile. Chouchou va vers la porte. Il va vers eux. Il va vers maman. Maman est dans le salon. Le canapé est mou. Maman. J'ai besoin du bocal. Je t'écoute, Chouchou. Tu as dit le besoin. Maman vient. Maman donne le bocal. Le bocal est lourd. Les noix sentent bon. Merci, maman. Bravo. Tu es venu vers moi. On peut aller vers eux. On peut dire le besoin. On peut appeler papa ou maman. Chouchou ouvre le bocal. Une noix est lisse. Une noix est un peu rêche. Tu poses une noix ? Oui, maman. Chouchou pose une noix. Elle fait un petit bruit. C'est la même noix ? Non. Une autre. Tu as dit le besoin. Le bocal est là. Le rideau beige ne bouge pas. La tasse bleue attend encore. Tu veux un peu d'eau ? Oui. L'eau est fraîche. Chouchou boit une gorgée. La noix sous la chaise, tu la prends ? Oui, papa. Chouchou ramasse la noix. Elle est ronde et un peu froide. Tu la mets avec les autres ? Oui, maman. Chouchou pose la noix dans le bocal. Ça fait un petit bruit. Bravo, Chouchou. Tu as dit le besoin. Le bocal est là.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hippolyte n'arrive pas. Que fait-il ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou n'arrive pas. Que fait-il ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là. Tu es venu me le dire. Bravo. C'est du bon travail, Chouchou. Tu as fini ta noix ? Oui, papa. La noix sous la chaise est encore là. Elle ne roule plus.</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là. Tu es venu me le dire. Bravo. Tu as fini ta noix ? Oui, papa. La noix sous la chaise est encore là. Elle ne roule plus.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hippolyte a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a appelé. Il a dit le besoin. Maman a entendu. Le bocal est là. Tu es venu me le dire. Bravo. Tu as fini ta noix ? Oui, papa. La noix sous la chaise est encore là. Elle ne roule plus.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1746,7 +1746,6 @@
 narrateur|Le bocal est là.
 maman|Tu es venu me le dire.
 maman|Bravo.
-papa|C'est du bon travail, Chouchou.
 papa|Tu as fini ta noix ?
 enfant-m|Oui, papa.
 narrateur|La noix sous la chaise est encore là.
@@ -1782,7 +1781,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Hippolyte pose une noix. Maman s'assoit près de lui.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou pose une noix. Maman s'assoit près de lui. Elle est lisse ? Oui. Lisse. On range le bocal après ? Oui, papa. Le bocal est lourd. Les noix sentent encore bon. On reste un peu ensemble ? Oui. La cuisine est tiède. La tasse bleue brille. On referme le bocal ensemble ? Oui, papa. Papa tient le bocal. Chouchou pose le couvercle. C'est bien. On a fini.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1956,12 +1955,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Chouchou. Tu as fait du bon travail. La noix ne roule plus. L'histoire est finie.</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Chouchou. La noix ne roule plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit le besoin. Oui. Tu es venu vers moi. Bravo, Chouchou. La noix ne roule plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2099,9 +2098,7 @@
           <t>enfant-m|J'ai dit le besoin.
 maman|Oui. Tu es venu vers moi.
 papa|Bravo, Chouchou.
-papa|Tu as fait du bon travail.
-narrateur|La noix ne roule plus.
-narrateur|L'histoire est finie.</t>
+narrateur|La noix ne roule plus.</t>
         </is>
       </c>
     </row>
@@ -2122,7 +2119,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2167,6 +2164,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-FAM.AID.001-08.xlsx
+++ b/stories/arbres/ATOM-FAM.AID.001-08.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>cuisine</t>
+          <t>cuisine puis salon</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hippolyte, maman</t>
+          <t>Chouchou, maman, papa</t>
         </is>
       </c>
     </row>
